--- a/reports/二级子公司D_利润表_2026-04.xlsx
+++ b/reports/二级子公司D_利润表_2026-04.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>85129588</v>
+        <v>87836678</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>83230892</v>
+        <v>84104122</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>314135289</v>
+        <v>314823106</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>287233</v>
+        <v>288323</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1083426</v>
+        <v>1087986</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>246289</v>
+        <v>246532</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>928692</v>
+        <v>931726</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>207089</v>
+        <v>205040</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>775463</v>
+        <v>775414</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>185754</v>
+        <v>184324</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>697416</v>
+        <v>696814</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>102389</v>
+        <v>102390</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>386769</v>
+        <v>386559</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>82407</v>
+        <v>81988</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>309822</v>
+        <v>308901</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>84018427</v>
+        <v>86728081</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>82119731</v>
+        <v>82995525</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4610860</v>
+        <v>4642796</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>17407167</v>
+        <v>17377462</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>361874</v>
+        <v>361905</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>1356606</v>
+        <v>1353157</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>620427</v>
+        <v>621353</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>2325755</v>
+        <v>2323101</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>73779497</v>
+        <v>74604882</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>278526243</v>
+        <v>279192627</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1233275</v>
+        <v>1242819</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4644973</v>
+        <v>4659191</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>414419</v>
+        <v>413675</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1551139</v>
+        <v>1554363</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2060478</v>
+        <v>2063908</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>7746185</v>
+        <v>7773701</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>511936</v>
+        <v>514689</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>1933827</v>
+        <v>1942661</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1857275</v>
+        <v>1848438</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>6973625</v>
+        <v>6986856</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>41421</v>
+        <v>40999</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>165009</v>
+        <v>164989</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1105861</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>4180043</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>737258</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>2782752</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>55874702</v>
+        <v>60124690</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>50079781</v>
+        <v>50344491</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>49153285</v>
+        <v>49415634</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>185655308</v>
+        <v>185247375</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>926496</v>
+        <v>928857</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>3485015</v>
+        <v>3475943</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1861688</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>6960365</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>596579</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2230632</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>373023</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1396227</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>447352</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1677546</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>334992</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1259121</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>222830</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>839546</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>185226</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>699289</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>880500</v>
+        <v>872622</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>3296045</v>
+        <v>3298812</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>670071</v>
+        <v>666114</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2517858</v>
+        <v>2519097</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>511911</v>
+        <v>511943</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>1933811</v>
+        <v>1934817</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3918548</v>
+        <v>3891411</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>14720105</v>
+        <v>14684304</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>155366</v>
+        <v>153791</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>618800</v>
+        <v>579067</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>328596</v>
+        <v>328742</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1317767</v>
+        <v>1313675</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>369100</v>
+        <v>328742</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1481517</v>
+        <v>1313675</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>41389</v>
+        <v>41296</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>164942</v>
+        <v>164342</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>167592</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>666386</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>326292</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1220125</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>111905</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>445580</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>83865</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>334601</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>139543</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>558106</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>464077</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1749007</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>74066</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>297576</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>55422</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>222958</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>92215</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>371082</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>64502</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>259362</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>46087</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>185002</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>36918</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>147851</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27746</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>110838</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>28143725</v>
+        <v>27745904</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>32337796</v>
+        <v>30776205</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>186254</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>696301</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>46618</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>185419</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>72400</v>
+        <v>72528</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>288618</v>
+        <v>288856</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>28071325</v>
+        <v>27859630</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2561206</v>
+        <v>2583409</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>10288974</v>
+        <v>10335918</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>25510119</v>
+        <v>25276221</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>25510119</v>
+        <v>25276221</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>25510119</v>
+        <v>25276221</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>25510119</v>
+        <v>25276221</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>25510119</v>
+        <v>25276221</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
